--- a/exports/treasury/treasury_curveTradesRecap_hitRate.xlsx
+++ b/exports/treasury/treasury_curveTradesRecap_hitRate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/riccardo/Desktop/Personal Projects/Latest/Yield curve models/gauss+/exports/treasury/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD7FDFC-3162-6C45-BC2D-3C12F3E060E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEAC99D-CCCF-0B40-909A-3FF5431A75CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5840" yWindow="680" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <t>Source: BSIC</t>
   </si>
   <si>
-    <t>U.S. Treasuries, hit rates</t>
+    <t>U.S. Treasuries, average hit rate</t>
   </si>
 </sst>
 </file>
@@ -194,7 +194,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -564,7 +564,7 @@
         <v>0.52590000000000003</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
@@ -577,7 +577,7 @@
         <v>0.57579999999999998</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
